--- a/basedatos_partidas/salida/descompuestos/09.07.01.190.xlsx
+++ b/basedatos_partidas/salida/descompuestos/09.07.01.190.xlsx
@@ -558,10 +558,10 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>39.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>55.2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -743,10 +743,10 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>70.15000000000001</v>
+        <v>74.95</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="22">
@@ -762,7 +762,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>70.84999999999999</v>
+        <v>75.7</v>
       </c>
     </row>
   </sheetData>
